--- a/LISTAS/mi/TARUGOS.xlsx
+++ b/LISTAS/mi/TARUGOS.xlsx
@@ -943,7 +943,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45184.56809757094</v>
+        <v>45219</v>
       </c>
       <c r="H1" s="19" t="n"/>
     </row>
@@ -1018,7 +1018,6 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="35.25" customHeight="1" s="22">
       <c r="A10" s="21" t="inlineStr">
         <is>
@@ -1033,27 +1032,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="27.75" customHeight="1" s="22" thickBot="1">
       <c r="B33" s="38" t="inlineStr">
         <is>
@@ -1101,7 +1079,7 @@
         <v>1000</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1462</v>
+        <v>1608.2</v>
       </c>
       <c r="H35" s="41" t="n"/>
       <c r="I35" s="12" t="n"/>
@@ -1123,7 +1101,7 @@
         <v>1000</v>
       </c>
       <c r="D36" s="9" t="n">
-        <v>1462</v>
+        <v>1608.2</v>
       </c>
       <c r="H36" s="41" t="n"/>
       <c r="J36" s="11" t="n"/>
@@ -1144,7 +1122,7 @@
         <v>500</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1462</v>
+        <v>1800</v>
       </c>
       <c r="H37" s="41" t="n"/>
       <c r="J37" s="11" t="n"/>
@@ -1165,7 +1143,7 @@
         <v>250</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1462</v>
+        <v>1608.2</v>
       </c>
       <c r="H38" s="41" t="n"/>
       <c r="J38" s="11" t="n"/>
@@ -1186,7 +1164,7 @@
         <v>250</v>
       </c>
       <c r="D39" s="33" t="n">
-        <v>4163</v>
+        <v>4579.3</v>
       </c>
       <c r="H39" s="41" t="n"/>
       <c r="I39" s="12" t="n"/>
@@ -1241,7 +1219,7 @@
         <v>1000</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1576.3</v>
+        <v>1733.93</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="22">
@@ -1259,7 +1237,7 @@
         <v>1000</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1576.3</v>
+        <v>1733.93</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="22">
@@ -1277,7 +1255,7 @@
         <v>500</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1576.3</v>
+        <v>1733.93</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1" s="22" thickBot="1">
@@ -1295,7 +1273,7 @@
         <v>250</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>1576.3</v>
+        <v>1733.93</v>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1" s="22" thickBot="1">
@@ -1313,12 +1291,9 @@
         <v>250</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>4656</v>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
+        <v>5121.6</v>
+      </c>
+    </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -1335,11 +1310,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B40:D40"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TARUGOS.xlsx
+++ b/LISTAS/mi/TARUGOS.xlsx
@@ -943,7 +943,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45219</v>
+        <v>45253</v>
       </c>
       <c r="H1" s="19" t="n"/>
     </row>
@@ -1310,10 +1310,10 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B40:D40"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>

--- a/LISTAS/mi/TARUGOS.xlsx
+++ b/LISTAS/mi/TARUGOS.xlsx
@@ -943,7 +943,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="H1" s="19" t="n"/>
     </row>

--- a/LISTAS/mi/TARUGOS.xlsx
+++ b/LISTAS/mi/TARUGOS.xlsx
@@ -943,7 +943,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="H1" s="19" t="n"/>
     </row>

--- a/LISTAS/mi/TARUGOS.xlsx
+++ b/LISTAS/mi/TARUGOS.xlsx
@@ -943,7 +943,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="H1" s="19" t="n"/>
     </row>

--- a/LISTAS/mi/TARUGOS.xlsx
+++ b/LISTAS/mi/TARUGOS.xlsx
@@ -943,7 +943,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="H1" s="19" t="n"/>
     </row>

--- a/LISTAS/mi/TARUGOS.xlsx
+++ b/LISTAS/mi/TARUGOS.xlsx
@@ -943,7 +943,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45266</v>
+        <v>45257.5565236745</v>
       </c>
       <c r="H1" s="19" t="n"/>
     </row>
@@ -1018,6 +1018,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="35.25" customHeight="1" s="22">
       <c r="A10" s="21" t="inlineStr">
         <is>
@@ -1032,6 +1033,27 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33" ht="27.75" customHeight="1" s="22" thickBot="1">
       <c r="B33" s="38" t="inlineStr">
         <is>
@@ -1079,7 +1101,7 @@
         <v>1000</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1608.2</v>
+        <v>2330.86</v>
       </c>
       <c r="H35" s="41" t="n"/>
       <c r="I35" s="12" t="n"/>
@@ -1101,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="D36" s="9" t="n">
-        <v>1608.2</v>
+        <v>2330.86</v>
       </c>
       <c r="H36" s="41" t="n"/>
       <c r="J36" s="11" t="n"/>
@@ -1122,7 +1144,7 @@
         <v>500</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1800</v>
+        <v>2330.86</v>
       </c>
       <c r="H37" s="41" t="n"/>
       <c r="J37" s="11" t="n"/>
@@ -1143,7 +1165,7 @@
         <v>250</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1608.2</v>
+        <v>2330.86</v>
       </c>
       <c r="H38" s="41" t="n"/>
       <c r="J38" s="11" t="n"/>
@@ -1164,7 +1186,7 @@
         <v>250</v>
       </c>
       <c r="D39" s="33" t="n">
-        <v>4579.3</v>
+        <v>6637.05</v>
       </c>
       <c r="H39" s="41" t="n"/>
       <c r="I39" s="12" t="n"/>
@@ -1219,7 +1241,7 @@
         <v>1000</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1733.93</v>
+        <v>2513.08</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="22">
@@ -1237,7 +1259,7 @@
         <v>1000</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1733.93</v>
+        <v>2513.08</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="22">
@@ -1255,7 +1277,7 @@
         <v>500</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1733.93</v>
+        <v>2513.08</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1" s="22" thickBot="1">
@@ -1273,7 +1295,7 @@
         <v>250</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>1733.93</v>
+        <v>2513.08</v>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1" s="22" thickBot="1">
@@ -1291,9 +1313,12 @@
         <v>250</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>5121.6</v>
-      </c>
-    </row>
+        <v>7423.04</v>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -1310,11 +1335,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
